--- a/experiments/20250728_binary/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250728_binary/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0728\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6390D831-50C9-49C8-A0D2-60C216443C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1108359-C4AF-433E-A712-88FDB2F82516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1080" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
-    <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Plate 2 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="MethodPointer1">-753954128</definedName>
@@ -55,7 +55,7 @@
     <t>Plate Number</t>
   </si>
   <si>
-    <t>Plate 1</t>
+    <t>Plate 2</t>
   </si>
   <si>
     <t>Date</t>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,61 +193,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD8E9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FA9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABCEEA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DBCE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF9CC5E5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7EB2DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3385C2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBAD7EF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFABCEEA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7EB2DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FA9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8E9F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DBCE0"/>
+        <fgColor rgb="FF60A0D1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5197CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC9E0F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3385C2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -298,12 +310,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -329,6 +341,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -686,7 +704,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45866</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -694,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.52930555555555558</v>
+        <v>0.38704861111111111</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -774,7 +792,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -824,7 +842,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="D25" s="7">
-        <v>4.3999999999999997E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="E25" s="7">
         <v>4.4999999999999998E-2</v>
@@ -842,10 +860,10 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="J25" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="K25" s="7">
-        <v>4.1000000000000002E-2</v>
+        <v>3.9E-2</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0.22800000000000001</v>
       </c>
       <c r="L25" s="7">
         <v>4.2000000000000003E-2</v>
@@ -856,7 +874,7 @@
       <c r="N25" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="9">
         <v>600</v>
       </c>
     </row>
@@ -868,7 +886,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="D26" s="7">
-        <v>4.3999999999999997E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="E26" s="7">
         <v>0.04</v>
@@ -877,7 +895,7 @@
         <v>0.04</v>
       </c>
       <c r="G26" s="7">
-        <v>4.2999999999999997E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="H26" s="7">
         <v>3.9E-2</v>
@@ -891,16 +909,16 @@
       <c r="K26" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="L26" s="9">
-        <v>1.169</v>
-      </c>
-      <c r="M26" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="N26" s="11">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="O26" s="8">
+      <c r="L26" s="10">
+        <v>1.492</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="N26" s="12">
+        <v>1.208</v>
+      </c>
+      <c r="O26" s="9">
         <v>600</v>
       </c>
     </row>
@@ -918,33 +936,33 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="F27" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="G27" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>0.04</v>
       </c>
       <c r="H27" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I27" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="J27" s="9">
-        <v>1.155</v>
-      </c>
-      <c r="K27" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="L27" s="11">
-        <v>0.97099999999999997</v>
-      </c>
-      <c r="M27" s="12">
-        <v>1.536</v>
-      </c>
-      <c r="N27" s="13">
-        <v>1.72</v>
-      </c>
-      <c r="O27" s="8">
+      <c r="J27" s="12">
+        <v>1.163</v>
+      </c>
+      <c r="K27" s="13">
+        <v>1.0589999999999999</v>
+      </c>
+      <c r="L27" s="14">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="M27" s="15">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="N27" s="16">
+        <v>2.524</v>
+      </c>
+      <c r="O27" s="9">
         <v>600</v>
       </c>
     </row>
@@ -962,33 +980,33 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="F28" s="7">
-        <v>0.24099999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="G28" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="H28" s="14">
-        <v>0.25600000000000001</v>
+        <v>0.128</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0.23100000000000001</v>
       </c>
       <c r="I28" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>0.04</v>
       </c>
       <c r="J28" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="K28" s="7">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="L28" s="14">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="M28" s="7">
-        <v>0.24099999999999999</v>
+        <v>0.187</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0.27400000000000002</v>
       </c>
       <c r="N28" s="7">
-        <v>8.1000000000000003E-2</v>
-      </c>
-      <c r="O28" s="8">
+        <v>6.2E-2</v>
+      </c>
+      <c r="O28" s="9">
         <v>600</v>
       </c>
     </row>
@@ -1005,34 +1023,34 @@
       <c r="E29" s="7">
         <v>0.04</v>
       </c>
-      <c r="F29" s="9">
-        <v>1.1619999999999999</v>
-      </c>
-      <c r="G29" s="15">
-        <v>1.363</v>
-      </c>
-      <c r="H29" s="11">
-        <v>1.0009999999999999</v>
+      <c r="F29" s="14">
+        <v>1.3120000000000001</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1.387</v>
+      </c>
+      <c r="H29" s="12">
+        <v>1.236</v>
       </c>
       <c r="I29" s="7">
-        <v>0.04</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="J29" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="K29" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="L29" s="16">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="M29" s="11">
-        <v>0.97099999999999997</v>
-      </c>
-      <c r="N29" s="10">
-        <v>0.84199999999999997</v>
-      </c>
-      <c r="O29" s="8">
+        <v>0.114</v>
+      </c>
+      <c r="L29" s="17">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="M29" s="14">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="N29" s="13">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="O29" s="9">
         <v>600</v>
       </c>
     </row>
@@ -1040,43 +1058,43 @@
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="15">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="D30" s="17">
-        <v>2.5230000000000001</v>
-      </c>
-      <c r="E30" s="17">
-        <v>2.5449999999999999</v>
-      </c>
-      <c r="F30" s="14">
-        <v>0.442</v>
-      </c>
-      <c r="G30" s="14">
-        <v>0.317</v>
-      </c>
-      <c r="H30" s="16">
-        <v>0.54900000000000004</v>
-      </c>
-      <c r="I30" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="J30" s="17">
-        <v>2.589</v>
-      </c>
-      <c r="K30" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="L30" s="13">
-        <v>1.873</v>
-      </c>
-      <c r="M30" s="18">
-        <v>2.9009999999999998</v>
-      </c>
-      <c r="N30" s="18">
-        <v>2.9239999999999999</v>
-      </c>
-      <c r="O30" s="8">
+      <c r="C30" s="18">
+        <v>1.7030000000000001</v>
+      </c>
+      <c r="D30" s="19">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="E30" s="19">
+        <v>2.0219999999999998</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0.315</v>
+      </c>
+      <c r="H30" s="20">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0.63</v>
+      </c>
+      <c r="J30" s="16">
+        <v>2.5790000000000002</v>
+      </c>
+      <c r="K30" s="18">
+        <v>1.7729999999999999</v>
+      </c>
+      <c r="L30" s="18">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="M30" s="15">
+        <v>2.242</v>
+      </c>
+      <c r="N30" s="15">
+        <v>2.2909999999999999</v>
+      </c>
+      <c r="O30" s="9">
         <v>600</v>
       </c>
     </row>
@@ -1093,23 +1111,23 @@
       <c r="E31" s="7">
         <v>0.04</v>
       </c>
-      <c r="F31" s="16">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G31" s="14">
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="H31" s="16">
-        <v>0.57999999999999996</v>
+      <c r="F31" s="11">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.623</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.83399999999999996</v>
       </c>
       <c r="I31" s="7">
-        <v>0.11</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="J31" s="7">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="K31" s="7">
-        <v>0.14499999999999999</v>
+        <v>0.107</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0.39800000000000002</v>
       </c>
       <c r="L31" s="7">
         <v>0.04</v>
@@ -1118,9 +1136,9 @@
         <v>3.9E-2</v>
       </c>
       <c r="N31" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="O31" s="8">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O31" s="9">
         <v>600</v>
       </c>
     </row>
@@ -1137,14 +1155,14 @@
       <c r="E32" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F32" s="7">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="G32" s="7">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="H32" s="7">
-        <v>0.10199999999999999</v>
+      <c r="F32" s="8">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0.39400000000000002</v>
       </c>
       <c r="I32" s="7">
         <v>4.1000000000000002E-2</v>
@@ -1153,7 +1171,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="K32" s="7">
-        <v>0.04</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="L32" s="7">
         <v>3.9E-2</v>
@@ -1162,9 +1180,9 @@
         <v>3.9E-2</v>
       </c>
       <c r="N32" s="7">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="O32" s="8">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="O32" s="9">
         <v>600</v>
       </c>
     </row>
